--- a/ONCHO/Impact Assessments/Eq Guinea/gq_oncho_ia_2507_2_questions.xlsx
+++ b/ONCHO/Impact Assessments/Eq Guinea/gq_oncho_ia_2507_2_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Impact Assessments\Eq Guinea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926EC3C1-5E45-4255-B8A0-2D0CAB65588A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E37DB39-E4AD-4FC8-88E6-319EB8C3FFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -734,9 +734,6 @@
     <t>${p_consent} = 'Sí' and ${p_id_type} = 'Escáner'</t>
   </si>
   <si>
-    <t>if(${p_id_type} = 'Escáner', concat(${p_barecode_id}), concat(${p_manual_id}))</t>
-  </si>
-  <si>
     <t>${p_consent} = 'Sí' and (${p_age_yrs_tranche} = '1 a 4 años')</t>
   </si>
   <si>
@@ -798,6 +795,9 @@
   </si>
   <si>
     <t>col_4</t>
+  </si>
+  <si>
+    <t>if(${p_id_type} = 'Escáner', concat(${p_barecode_id}), concat(${p_site_id}, '_', ${p_manual_id}))</t>
   </si>
 </sst>
 </file>
@@ -1498,7 +1498,7 @@
         <v>180</v>
       </c>
       <c r="U1" s="50" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V1" s="50"/>
     </row>
@@ -1544,14 +1544,14 @@
         <v>67</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D3" s="43"/>
       <c r="E3" s="17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="10"/>
@@ -1574,14 +1574,14 @@
         <v>67</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D4" s="43"/>
       <c r="E4" s="17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="12"/>
@@ -1599,7 +1599,7 @@
         <v>182</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1632,7 +1632,7 @@
         <v>183</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:22" s="1" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
@@ -1662,7 +1662,7 @@
       <c r="N6" s="10"/>
       <c r="O6" s="11"/>
       <c r="R6" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="U6" s="1" t="s">
         <v>184</v>
@@ -1726,7 +1726,7 @@
         <v>140</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C9" s="39" t="s">
         <v>161</v>
@@ -1917,7 +1917,7 @@
       <c r="N15" s="10"/>
       <c r="O15" s="10"/>
     </row>
-    <row r="16" spans="1:22" s="1" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" s="1" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>67</v>
       </c>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="K16" s="22"/>
       <c r="L16" s="10" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="M16" s="6"/>
       <c r="N16" s="10"/>
@@ -2031,7 +2031,7 @@
       <c r="I19" s="40"/>
       <c r="J19" s="13"/>
       <c r="K19" s="22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L19" s="10"/>
       <c r="M19" s="6" t="s">
@@ -2060,7 +2060,7 @@
       <c r="I20" s="40"/>
       <c r="J20" s="13"/>
       <c r="K20" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L20" s="10"/>
       <c r="M20" s="6" t="s">
@@ -2089,7 +2089,7 @@
       <c r="I21" s="40"/>
       <c r="J21" s="13"/>
       <c r="K21" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L21" s="10"/>
       <c r="M21" s="6" t="s">
@@ -2120,7 +2120,7 @@
       <c r="I22" s="40"/>
       <c r="J22" s="13"/>
       <c r="K22" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L22" s="10"/>
       <c r="M22" s="6" t="s">
@@ -2149,7 +2149,7 @@
       <c r="I23" s="40"/>
       <c r="J23" s="13"/>
       <c r="K23" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L23" s="10"/>
       <c r="M23" s="6" t="s">
@@ -2178,7 +2178,7 @@
       <c r="I24" s="40"/>
       <c r="J24" s="13"/>
       <c r="K24" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L24" s="10"/>
       <c r="M24" s="6" t="s">
@@ -2265,7 +2265,7 @@
       <c r="I27" s="40"/>
       <c r="J27" s="13"/>
       <c r="K27" s="22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L27" s="10"/>
       <c r="M27" s="6" t="s">
@@ -2323,7 +2323,7 @@
       <c r="I29" s="40"/>
       <c r="J29" s="13"/>
       <c r="K29" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L29" s="10"/>
       <c r="M29" s="6" t="s">
@@ -3511,10 +3511,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C2" t="s">
         <v>154</v>
